--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 20:09</t>
+    <t xml:space="preserve">2026-08-05 11:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 11:06</t>
+    <t xml:space="preserve">2026-08-16 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Antártica Chilena</t>
   </si>
   <si>
-    <t xml:space="preserve">Ultima Esperanza</t>
+    <t xml:space="preserve">Última Esperanza</t>
   </si>
   <si>
     <t xml:space="preserve">Magallanes</t>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:13</t>
+    <t xml:space="preserve">2026-08-19 14:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:40</t>
+    <t xml:space="preserve">2026-08-28 12:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_magallanes.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:37</t>
+    <t xml:space="preserve">2026-09-06 17:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
